--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -48,7 +48,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -78,7 +78,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -26,12 +26,15 @@
     <sheet name="Include #16" r:id="rId20" sheetId="18"/>
     <sheet name="Include #17" r:id="rId21" sheetId="19"/>
     <sheet name="Include #18" r:id="rId22" sheetId="20"/>
+    <sheet name="Include #19" r:id="rId23" sheetId="21"/>
+    <sheet name="Include #20" r:id="rId24" sheetId="22"/>
+    <sheet name="Exclude #21" r:id="rId25" sheetId="23"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -78,7 +81,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -183,6 +186,9 @@
     <t>LP6106-1</t>
   </si>
   <si>
+    <t>LP6429-7</t>
+  </si>
+  <si>
     <t>Concept</t>
   </si>
   <si>
@@ -196,6 +202,30 @@
   </si>
   <si>
     <t>Methicillin resistant Staphylococcus aureus (MRSA) DNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>44851-4</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 2 identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>44852-2</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 3 identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>44854-8</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 4 identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>44855-5</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 5 identified in Specimen by Organism specific culture</t>
   </si>
 </sst>
 </file>
@@ -1394,6 +1424,176 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1403,7 +1603,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -1411,18 +1611,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1438,6 +1638,76 @@
         <v>39</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>40</v>
       </c>
     </row>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -81,7 +81,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-spezifische-bestimmung-tests-loinc.xlsx
@@ -81,7 +81,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
